--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -7956,13 +7956,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O45" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R45" t="n">
-        <v>1.174014052770331</v>
+        <v>1.245166419604896</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O46" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11335</v>
+        <v>11341</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11341</v>
+        <v>11343</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11343</v>
+        <v>11348</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1048</v>
+        <v>1979</v>
       </c>
       <c r="O35" t="n">
-        <v>1048</v>
+        <v>1979</v>
       </c>
       <c r="R35" t="n">
-        <v>3.84910678685674</v>
+        <v>7.268494590829665</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1048</v>
+        <v>1979</v>
       </c>
       <c r="O36" t="n">
-        <v>1048</v>
+        <v>1979</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O50" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11348</v>
+        <v>12282</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="O24" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="R24" t="n">
-        <v>7.224420848995427</v>
+        <v>7.228093660814947</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="O25" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="O35" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="R35" t="n">
-        <v>7.268494590829665</v>
+        <v>7.261148967190626</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="O36" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12282</v>
+        <v>12281</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O49" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R49" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O50" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12281</v>
+        <v>12287</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O49" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R49" t="n">
-        <v>0.3557618341728275</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12287</v>
+        <v>12289</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="O24" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="R24" t="n">
-        <v>7.228093660814947</v>
+        <v>7.220748037175907</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="O25" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1977</v>
+        <v>1967</v>
       </c>
       <c r="O35" t="n">
-        <v>1977</v>
+        <v>1967</v>
       </c>
       <c r="R35" t="n">
-        <v>7.261148967190626</v>
+        <v>7.224420848995427</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1977</v>
+        <v>1967</v>
       </c>
       <c r="O36" t="n">
-        <v>1977</v>
+        <v>1967</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12289</v>
+        <v>12277</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="O24" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="R24" t="n">
-        <v>7.220748037175907</v>
+        <v>7.224420848995427</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="O25" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1967</v>
+        <v>1996</v>
       </c>
       <c r="O35" t="n">
-        <v>1967</v>
+        <v>1996</v>
       </c>
       <c r="R35" t="n">
-        <v>7.224420848995427</v>
+        <v>7.3309323917615</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1967</v>
+        <v>1996</v>
       </c>
       <c r="O36" t="n">
-        <v>1967</v>
+        <v>1996</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="O49" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="R49" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.6403713015110895</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="O50" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12277</v>
+        <v>12321</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -8349,13 +8349,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>104</v>
+        <v>1935</v>
       </c>
       <c r="O47" t="n">
-        <v>104</v>
+        <v>1935</v>
       </c>
       <c r="R47" t="n">
-        <v>0.3819724292300582</v>
+        <v>7.106890870770793</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>104</v>
+        <v>1935</v>
       </c>
       <c r="O48" t="n">
-        <v>104</v>
+        <v>1935</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="O49" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="R49" t="n">
-        <v>0.6403713015110895</v>
+        <v>1.013921227392558</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="O50" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9063,6 +9063,399 @@
         </is>
       </c>
       <c r="BC50" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -9101,7 +9494,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9577,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -9194,7 +9587,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -9214,7 +9607,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -9246,7 +9639,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12321</v>
+        <v>14173</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="O35" t="n">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="R35" t="n">
-        <v>7.3309323917615</v>
+        <v>7.345623639039581</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="O36" t="n">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -8349,13 +8349,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1935</v>
+        <v>1964</v>
       </c>
       <c r="O47" t="n">
-        <v>1935</v>
+        <v>1964</v>
       </c>
       <c r="R47" t="n">
-        <v>7.106890870770793</v>
+        <v>7.213402413536868</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1935</v>
+        <v>1964</v>
       </c>
       <c r="O48" t="n">
-        <v>1935</v>
+        <v>1964</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14173</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -8742,13 +8742,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O49" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R49" t="n">
-        <v>1.013921227392558</v>
+        <v>1.049497410809841</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O50" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9135,13 +9135,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9294,10 +9294,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14206</v>
+        <v>14210</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -26062,13 +26062,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="O131" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="R131" t="n">
-        <v>7.345623639039581</v>
+        <v>7.312568332663902</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -26221,10 +26221,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="O132" t="n">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -29992,13 +29992,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1939</v>
+        <v>1946</v>
       </c>
       <c r="O151" t="n">
-        <v>1939</v>
+        <v>1946</v>
       </c>
       <c r="R151" t="n">
-        <v>7.121582118048874</v>
+        <v>7.147291800785512</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -30151,10 +30151,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1939</v>
+        <v>1946</v>
       </c>
       <c r="O152" t="n">
-        <v>1939</v>
+        <v>1946</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -33922,13 +33922,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O171" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R171" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -34081,10 +34081,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O172" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25986</v>
+        <v>25989</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -26062,13 +26062,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="O131" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="R131" t="n">
-        <v>7.312568332663902</v>
+        <v>7.308895520844382</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -26221,10 +26221,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="O132" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -29992,13 +29992,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1946</v>
+        <v>1932</v>
       </c>
       <c r="O151" t="n">
-        <v>1946</v>
+        <v>1932</v>
       </c>
       <c r="R151" t="n">
-        <v>7.147291800785512</v>
+        <v>7.095872435312234</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -30151,10 +30151,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1946</v>
+        <v>1932</v>
       </c>
       <c r="O152" t="n">
-        <v>1946</v>
+        <v>1932</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -33922,13 +33922,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O171" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R171" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -34081,10 +34081,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O172" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25989</v>
+        <v>25980</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -29992,13 +29992,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="O151" t="n">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="R151" t="n">
-        <v>7.095872435312234</v>
+        <v>7.088526811673195</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -30151,10 +30151,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="O152" t="n">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -33922,13 +33922,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O171" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R171" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -34081,10 +34081,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O172" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25980</v>
+        <v>25982</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23945,7 +23945,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25517,7 +25517,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26696,7 +26696,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -27482,7 +27482,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27875,7 +27875,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -28268,7 +28268,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -29054,7 +29054,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -29447,7 +29447,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29992,13 +29992,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="O151" t="n">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="R151" t="n">
-        <v>7.088526811673195</v>
+        <v>7.066489940756076</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -30151,10 +30151,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="O152" t="n">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -31412,7 +31412,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -32198,7 +32198,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -33377,7 +33377,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -33529,13 +33529,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O169" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R169" t="n">
-        <v>1.049497410809841</v>
+        <v>1.067285502518482</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -33688,10 +33688,10 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O170" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
@@ -33922,13 +33922,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O171" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R171" t="n">
-        <v>0.3023975590469034</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -34081,10 +34081,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O172" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -12991,13 +12991,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O87" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R87" t="n">
-        <v>0.569218934676524</v>
+        <v>0.5870070263851653</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25992</v>
+        <v>25993</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -11551,13 +11551,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="O77" t="n">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="R77" t="n">
-        <v>7.066489940756076</v>
+        <v>7.062817128936556</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25993</v>
+        <v>25992</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -12991,13 +12991,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O87" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="R87" t="n">
-        <v>0.5870070263851653</v>
+        <v>0.7470998517629377</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25992</v>
+        <v>26001</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -11551,13 +11551,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1923</v>
+        <v>1920</v>
       </c>
       <c r="O77" t="n">
-        <v>1923</v>
+        <v>1920</v>
       </c>
       <c r="R77" t="n">
-        <v>7.062817128936556</v>
+        <v>7.051798693477997</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -12952,12 +12952,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12991,17 +12991,17 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>42</v>
+        <v>1595</v>
       </c>
       <c r="O87" t="n">
-        <v>42</v>
+        <v>1595</v>
       </c>
       <c r="R87" t="n">
-        <v>0.7470998517629377</v>
+        <v>5.858134852134065</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -13029,40 +13029,184 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>53</v>
+      </c>
+      <c r="O88" t="n">
+        <v>53</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.9427688605579929</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW87" t="inlineStr">
+      <c r="AW88" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
+      <c r="AX88" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY87" t="inlineStr">
+      <c r="AY88" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA87" t="inlineStr">
+      <c r="BA88" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB87" t="inlineStr">
+      <c r="BB88" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC87" t="inlineStr">
+      <c r="BC88" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -13184,7 +13328,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -13194,7 +13338,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -13246,7 +13390,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26001</v>
+        <v>27604</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -1920,6 +1920,11 @@
       <c r="R10" t="n">
         <v>0.7293117600542963</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1501</t>
@@ -1937,7 +1942,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -1947,6 +1957,11 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2012,17 +2027,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2047,26 +2062,48 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5.309720055221089</v>
+        <v>41</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2074,62 +2111,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2266,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2200,13 +2305,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>5.309720055221089</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2220,7 +2325,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2243,7 +2348,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2263,7 +2368,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -2305,12 +2410,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2344,13 +2449,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>5.578302634074504</v>
+        <v>0</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2364,7 +2469,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -2387,7 +2492,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2407,7 +2512,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -2449,12 +2554,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2488,13 +2593,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>612</v>
+        <v>15</v>
       </c>
       <c r="O14" t="n">
-        <v>612</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
-        <v>10.66302218971433</v>
+        <v>5.578302634074504</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2508,7 +2613,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -2531,7 +2636,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2551,7 +2656,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -2593,12 +2698,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2632,13 +2737,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>125</v>
+        <v>612</v>
       </c>
       <c r="O15" t="n">
-        <v>125</v>
+        <v>612</v>
       </c>
       <c r="R15" t="n">
-        <v>6.521162999860187</v>
+        <v>10.66302218971433</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2652,7 +2757,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -2675,7 +2780,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2695,7 +2800,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -2737,12 +2842,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2776,13 +2881,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="O16" t="n">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="R16" t="n">
-        <v>3.271963918848407</v>
+        <v>6.521162999860187</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2819,7 +2924,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2839,7 +2944,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -2881,12 +2986,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2920,13 +3025,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>866</v>
+        <v>19</v>
       </c>
       <c r="O17" t="n">
-        <v>866</v>
+        <v>19</v>
       </c>
       <c r="R17" t="n">
-        <v>12.10474208163265</v>
+        <v>3.271963918848407</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2963,7 +3068,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2983,7 +3088,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -3025,12 +3130,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3064,13 +3169,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>236</v>
+        <v>866</v>
       </c>
       <c r="O18" t="n">
-        <v>236</v>
+        <v>866</v>
       </c>
       <c r="R18" t="n">
-        <v>7.622192465527342</v>
+        <v>12.10474208163265</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3107,7 +3212,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -3127,7 +3232,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -3169,12 +3274,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3208,17 +3313,17 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="O19" t="n">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="R19" t="n">
-        <v>1.013921227392558</v>
+        <v>7.622192465527342</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3228,7 +3333,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -3238,7 +3343,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -3246,42 +3351,42 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3313,12 +3418,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3343,26 +3448,31 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="O20" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="R20" t="n">
-        <v>7.556140078583856</v>
+        <v>1.013921227392558</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3372,60 +3482,70 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT20" t="n">
         <v>1</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -3452,17 +3572,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3487,26 +3607,48 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3514,6 +3656,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3521,55 +3721,65 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT21" t="n">
         <v>1</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3811,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3640,13 +3850,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="R22" t="n">
-        <v>6.693963160889404</v>
+        <v>7.556140078583856</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3683,7 +3893,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3703,7 +3913,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -3745,12 +3955,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3784,13 +3994,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>12.00461158286466</v>
+        <v>0</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3827,7 +4037,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3847,7 +4057,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -3889,12 +4099,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3928,13 +4138,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="O24" t="n">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="R24" t="n">
-        <v>7.35587186384229</v>
+        <v>6.693963160889404</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3971,7 +4181,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3991,7 +4201,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -4033,12 +4243,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4072,13 +4282,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>26</v>
+        <v>689</v>
       </c>
       <c r="O25" t="n">
-        <v>26</v>
+        <v>689</v>
       </c>
       <c r="R25" t="n">
-        <v>4.477424310003082</v>
+        <v>12.00461158286466</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4092,7 +4302,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
@@ -4115,7 +4325,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -4135,7 +4345,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -4177,12 +4387,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4216,13 +4426,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>943</v>
+        <v>141</v>
       </c>
       <c r="O26" t="n">
-        <v>943</v>
+        <v>141</v>
       </c>
       <c r="R26" t="n">
-        <v>13.18102977249375</v>
+        <v>7.35587186384229</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -4259,7 +4469,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -4279,7 +4489,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -4321,12 +4531,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4360,13 +4570,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="O27" t="n">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="R27" t="n">
-        <v>7.460705337020407</v>
+        <v>4.477424310003082</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4403,7 +4613,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4423,7 +4633,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -4465,12 +4675,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4504,17 +4714,17 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>64</v>
+        <v>943</v>
       </c>
       <c r="O28" t="n">
-        <v>64</v>
+        <v>943</v>
       </c>
       <c r="R28" t="n">
-        <v>1.138437869353048</v>
+        <v>13.18102977249375</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4524,7 +4734,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -4534,7 +4744,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -4542,42 +4752,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4819,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4639,22 +4849,22 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>28</v>
+        <v>231</v>
       </c>
       <c r="O29" t="n">
-        <v>28</v>
+        <v>231</v>
       </c>
       <c r="R29" t="n">
-        <v>5.718160059468865</v>
+        <v>7.460705337020407</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4691,7 +4901,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -4711,7 +4921,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -4753,12 +4963,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4783,26 +4993,31 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.138437869353048</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4817,55 +5032,65 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT30" t="n">
         <v>1</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -4892,17 +5117,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4927,26 +5152,48 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="O31" t="n">
-        <v>24</v>
-      </c>
-      <c r="R31" t="n">
-        <v>8.925284214519206</v>
+        <v>64</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4954,62 +5201,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT31" t="n">
         <v>1</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -5041,12 +5356,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5080,13 +5395,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>541</v>
+        <v>28</v>
       </c>
       <c r="O32" t="n">
-        <v>541</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
-        <v>9.425972229796491</v>
+        <v>5.718160059468865</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -5100,7 +5415,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
@@ -5123,7 +5438,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -5143,7 +5458,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -5185,12 +5500,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5224,13 +5539,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.364655087863541</v>
+        <v>0</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -5244,7 +5559,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
@@ -5267,7 +5582,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -5287,7 +5602,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -5329,12 +5644,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5368,13 +5683,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O34" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R34" t="n">
-        <v>3.444172546156217</v>
+        <v>8.925284214519206</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5411,7 +5726,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -5431,7 +5746,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -5473,12 +5788,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5512,13 +5827,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>833</v>
+        <v>541</v>
       </c>
       <c r="O35" t="n">
-        <v>833</v>
+        <v>541</v>
       </c>
       <c r="R35" t="n">
-        <v>11.64347592840646</v>
+        <v>9.425972229796491</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5532,7 +5847,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
@@ -5555,7 +5870,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -5575,7 +5890,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -5617,12 +5932,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5656,13 +5971,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>218</v>
+        <v>122</v>
       </c>
       <c r="O36" t="n">
-        <v>218</v>
+        <v>122</v>
       </c>
       <c r="R36" t="n">
-        <v>7.040838802902376</v>
+        <v>6.364655087863541</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5699,7 +6014,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -5719,7 +6034,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -5761,12 +6076,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5800,17 +6115,17 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="O37" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="R37" t="n">
-        <v>0.9427688605579929</v>
+        <v>3.444172546156217</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5820,7 +6135,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
@@ -5830,7 +6145,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -5838,42 +6153,42 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5905,12 +6220,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5935,22 +6250,22 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>29</v>
+        <v>833</v>
       </c>
       <c r="O38" t="n">
-        <v>29</v>
+        <v>833</v>
       </c>
       <c r="R38" t="n">
-        <v>5.922380061592753</v>
+        <v>11.64347592840646</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5987,7 +6302,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -6007,7 +6322,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -6049,12 +6364,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6079,22 +6394,22 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>7.040838802902376</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6108,7 +6423,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
@@ -6131,7 +6446,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -6151,7 +6466,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -6193,12 +6508,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6223,26 +6538,31 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="O40" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="R40" t="n">
-        <v>6.322076318617771</v>
+        <v>0.9427688605579929</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6252,60 +6572,70 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT40" t="n">
         <v>1</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6662,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6367,26 +6697,48 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>620</v>
+        <v>53</v>
       </c>
       <c r="O41" t="n">
-        <v>620</v>
-      </c>
-      <c r="R41" t="n">
-        <v>10.80240810069099</v>
+        <v>53</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6394,6 +6746,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -6401,55 +6811,65 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT41" t="n">
         <v>1</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -6481,12 +6901,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6520,13 +6940,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="O42" t="n">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="R42" t="n">
-        <v>7.042856039849001</v>
+        <v>5.922380061592753</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6563,7 +6983,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -6583,7 +7003,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -6625,12 +7045,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6664,13 +7084,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.099755291540595</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -6684,7 +7104,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
@@ -6707,7 +7127,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -6727,7 +7147,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -6769,12 +7189,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6808,13 +7228,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>921</v>
+        <v>17</v>
       </c>
       <c r="O44" t="n">
-        <v>921</v>
+        <v>17</v>
       </c>
       <c r="R44" t="n">
-        <v>12.87351900367629</v>
+        <v>6.322076318617771</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6851,7 +7271,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6871,7 +7291,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -6913,12 +7333,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6952,13 +7372,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>246</v>
+        <v>620</v>
       </c>
       <c r="O45" t="n">
-        <v>246</v>
+        <v>620</v>
       </c>
       <c r="R45" t="n">
-        <v>7.945166722541214</v>
+        <v>10.80240810069099</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -6972,7 +7392,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
@@ -6995,7 +7415,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -7015,7 +7435,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -7057,12 +7477,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7096,17 +7516,17 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="O46" t="n">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="R46" t="n">
-        <v>1.013921227392558</v>
+        <v>7.042856039849001</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7116,7 +7536,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
@@ -7126,7 +7546,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -7134,42 +7554,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7201,12 +7621,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7231,22 +7651,22 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1979</v>
+        <v>18</v>
       </c>
       <c r="O47" t="n">
-        <v>1979</v>
+        <v>18</v>
       </c>
       <c r="R47" t="n">
-        <v>7.268494590829665</v>
+        <v>3.099755291540595</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7260,7 +7680,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
@@ -7283,12 +7703,12 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -7303,12 +7723,12 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -7345,12 +7765,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7375,22 +7795,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>32</v>
+        <v>921</v>
       </c>
       <c r="O48" t="n">
-        <v>32</v>
+        <v>921</v>
       </c>
       <c r="R48" t="n">
-        <v>6.535040067964417</v>
+        <v>12.87351900367629</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7427,7 +7847,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -7447,7 +7867,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -7489,12 +7909,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7519,22 +7939,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.945166722541214</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7548,7 +7968,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
@@ -7571,7 +7991,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -7591,7 +8011,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -7633,12 +8053,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7663,26 +8083,31 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="O50" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="R50" t="n">
-        <v>4.462642107259603</v>
+        <v>1.013921227392558</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7692,60 +8117,70 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT50" t="n">
         <v>1</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -7772,17 +8207,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7807,26 +8242,48 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>642</v>
+        <v>57</v>
       </c>
       <c r="O51" t="n">
-        <v>642</v>
-      </c>
-      <c r="R51" t="n">
-        <v>11.1857193558768</v>
+        <v>57</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7834,6 +8291,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7841,55 +8356,65 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT51" t="n">
         <v>1</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -7921,12 +8446,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7960,13 +8485,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>128</v>
+        <v>1979</v>
       </c>
       <c r="O52" t="n">
-        <v>128</v>
+        <v>1979</v>
       </c>
       <c r="R52" t="n">
-        <v>6.677670911856831</v>
+        <v>7.268494590829665</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7980,7 +8505,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
@@ -8003,12 +8528,12 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -8023,12 +8548,12 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -8065,12 +8590,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8104,13 +8629,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="O53" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="R53" t="n">
-        <v>3.96079842807965</v>
+        <v>6.535040067964417</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -8147,7 +8672,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -8167,7 +8692,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -8209,12 +8734,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8248,13 +8773,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>12.34236403935523</v>
+        <v>0</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8268,7 +8793,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
@@ -8291,7 +8816,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -8311,7 +8836,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -8353,12 +8878,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8392,13 +8917,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>261</v>
+        <v>12</v>
       </c>
       <c r="O55" t="n">
-        <v>261</v>
+        <v>12</v>
       </c>
       <c r="R55" t="n">
-        <v>8.429628108062019</v>
+        <v>4.462642107259603</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8435,7 +8960,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -8455,7 +8980,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -8497,12 +9022,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8536,17 +9061,17 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>58</v>
+        <v>642</v>
       </c>
       <c r="O56" t="n">
-        <v>58</v>
+        <v>642</v>
       </c>
       <c r="R56" t="n">
-        <v>1.0317093191012</v>
+        <v>11.1857193558768</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8566,7 +9091,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -8574,42 +9099,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8641,12 +9166,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8671,22 +9196,22 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1967</v>
+        <v>128</v>
       </c>
       <c r="O57" t="n">
-        <v>1967</v>
+        <v>128</v>
       </c>
       <c r="R57" t="n">
-        <v>7.224420848995427</v>
+        <v>6.677670911856831</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -8700,7 +9225,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
@@ -8723,12 +9248,12 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -8743,12 +9268,12 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -8785,12 +9310,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8815,22 +9340,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="O58" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R58" t="n">
-        <v>7.147700074336081</v>
+        <v>3.96079842807965</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -8867,7 +9392,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -8887,7 +9412,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -8929,12 +9454,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8959,22 +9484,22 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>12.34236403935523</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -8988,7 +9513,7 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
@@ -9011,7 +9536,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -9031,7 +9556,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -9073,12 +9598,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9103,13 +9628,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>261</v>
+      </c>
+      <c r="O60" t="n">
+        <v>261</v>
+      </c>
+      <c r="R60" t="n">
+        <v>8.429628108062019</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -9146,7 +9680,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -9166,7 +9700,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -9208,12 +9742,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9238,26 +9772,31 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>667</v>
+        <v>58</v>
       </c>
       <c r="O61" t="n">
-        <v>667</v>
+        <v>58</v>
       </c>
       <c r="R61" t="n">
-        <v>11.62130032767885</v>
+        <v>1.0317093191012</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9272,55 +9811,65 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT61" t="n">
         <v>1</v>
       </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9347,17 +9896,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9382,26 +9931,48 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="O62" t="n">
-        <v>128</v>
-      </c>
-      <c r="R62" t="n">
-        <v>6.677670911856831</v>
+        <v>58</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9409,62 +9980,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN62" t="b">
+        <v>1</v>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT62" t="n">
         <v>1</v>
       </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9496,12 +10135,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9535,13 +10174,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>25</v>
+        <v>1967</v>
       </c>
       <c r="O63" t="n">
-        <v>25</v>
+        <v>1967</v>
       </c>
       <c r="R63" t="n">
-        <v>4.305215682695271</v>
+        <v>7.224420848995427</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -9555,7 +10194,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
@@ -9578,12 +10217,12 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -9598,12 +10237,12 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -9640,12 +10279,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9679,13 +10318,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>855</v>
+        <v>35</v>
       </c>
       <c r="O64" t="n">
-        <v>855</v>
+        <v>35</v>
       </c>
       <c r="R64" t="n">
-        <v>11.95098669722392</v>
+        <v>7.147700074336081</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -9722,7 +10361,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -9742,7 +10381,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -9784,12 +10423,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9823,13 +10462,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>8.171248702450923</v>
+        <v>0</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -9843,7 +10482,7 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
@@ -9866,7 +10505,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -9886,7 +10525,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -9928,12 +10567,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9966,18 +10605,9 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="N66" t="n">
-        <v>69</v>
-      </c>
-      <c r="O66" t="n">
-        <v>69</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.227378327896255</v>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9987,7 +10617,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
@@ -9997,7 +10627,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -10005,42 +10635,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10702,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10102,22 +10732,22 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1990</v>
+        <v>667</v>
       </c>
       <c r="O67" t="n">
-        <v>1990</v>
+        <v>667</v>
       </c>
       <c r="R67" t="n">
-        <v>7.308895520844382</v>
+        <v>11.62130032767885</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10154,12 +10784,12 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -10174,12 +10804,12 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -10216,12 +10846,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10246,22 +10876,22 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="O68" t="n">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="R68" t="n">
-        <v>5.309720055221089</v>
+        <v>6.677670911856831</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10298,7 +10928,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -10318,7 +10948,7 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -10360,12 +10990,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10390,22 +11020,22 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4.305215682695271</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -10419,7 +11049,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
@@ -10442,7 +11072,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -10462,7 +11092,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -10504,12 +11134,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10534,22 +11164,22 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>10</v>
+        <v>855</v>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>855</v>
       </c>
       <c r="R70" t="n">
-        <v>3.718868422716336</v>
+        <v>11.95098669722392</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -10586,7 +11216,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -10606,7 +11236,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -10648,12 +11278,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10678,22 +11308,22 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>629</v>
+        <v>253</v>
       </c>
       <c r="O71" t="n">
-        <v>629</v>
+        <v>253</v>
       </c>
       <c r="R71" t="n">
-        <v>10.95921725053973</v>
+        <v>8.171248702450923</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -10707,7 +11337,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
@@ -10730,7 +11360,7 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -10750,7 +11380,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -10792,12 +11422,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10822,26 +11452,31 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="O72" t="n">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="R72" t="n">
-        <v>6.782009519854594</v>
+        <v>1.227378327896255</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10851,60 +11486,70 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT72" t="n">
         <v>1</v>
       </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -10931,17 +11576,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10966,26 +11611,48 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="O73" t="n">
-        <v>22</v>
-      </c>
-      <c r="R73" t="n">
-        <v>3.788589800771839</v>
+        <v>69</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10993,62 +11660,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT73" t="n">
         <v>1</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11080,12 +11815,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11119,13 +11854,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>903</v>
+        <v>1990</v>
       </c>
       <c r="O74" t="n">
-        <v>903</v>
+        <v>1990</v>
       </c>
       <c r="R74" t="n">
-        <v>12.62191928373474</v>
+        <v>7.308895520844382</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -11139,7 +11874,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
@@ -11162,12 +11897,12 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -11182,12 +11917,12 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -11224,12 +11959,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11263,13 +11998,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="O75" t="n">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="R75" t="n">
-        <v>9.043279196388374</v>
+        <v>5.309720055221089</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -11306,7 +12041,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -11326,7 +12061,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -11368,12 +12103,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11407,17 +12142,17 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.245166419604896</v>
+        <v>0</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11437,7 +12172,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -11445,42 +12180,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11512,12 +12247,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11542,22 +12277,22 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1920</v>
+        <v>10</v>
       </c>
       <c r="O77" t="n">
-        <v>1920</v>
+        <v>10</v>
       </c>
       <c r="R77" t="n">
-        <v>7.051798693477997</v>
+        <v>3.718868422716336</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -11571,7 +12306,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
@@ -11594,12 +12329,12 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -11614,12 +12349,12 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -11656,12 +12391,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11686,22 +12421,22 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>26</v>
+        <v>629</v>
       </c>
       <c r="O78" t="n">
-        <v>26</v>
+        <v>629</v>
       </c>
       <c r="R78" t="n">
-        <v>5.309720055221089</v>
+        <v>10.95921725053973</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -11715,7 +12450,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
@@ -11738,7 +12473,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -11758,7 +12493,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -11800,12 +12535,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11830,22 +12565,22 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>6.782009519854594</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -11859,7 +12594,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
@@ -11882,7 +12617,7 @@
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
@@ -11902,7 +12637,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -11944,12 +12679,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11974,22 +12709,22 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O80" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="R80" t="n">
-        <v>1.859434211358168</v>
+        <v>3.788589800771839</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -12026,7 +12761,7 @@
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -12046,7 +12781,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -12088,12 +12823,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12118,22 +12853,22 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>600</v>
+        <v>903</v>
       </c>
       <c r="O81" t="n">
-        <v>600</v>
+        <v>903</v>
       </c>
       <c r="R81" t="n">
-        <v>10.45394332324934</v>
+        <v>12.62191928373474</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -12147,7 +12882,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
@@ -12170,7 +12905,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -12190,7 +12925,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -12232,12 +12967,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12262,22 +12997,22 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>164</v>
+        <v>280</v>
       </c>
       <c r="O82" t="n">
-        <v>164</v>
+        <v>280</v>
       </c>
       <c r="R82" t="n">
-        <v>8.555765855816565</v>
+        <v>9.043279196388374</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -12314,7 +13049,7 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -12334,7 +13069,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -12376,12 +13111,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12406,26 +13141,31 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="O83" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="R83" t="n">
-        <v>4.477424310003082</v>
+        <v>1.245166419604896</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12435,60 +13175,70 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT83" t="n">
         <v>1</v>
       </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12515,17 +13265,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12550,26 +13300,48 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>861</v>
+        <v>70</v>
       </c>
       <c r="O84" t="n">
-        <v>861</v>
-      </c>
-      <c r="R84" t="n">
-        <v>12.03485327053777</v>
+        <v>70</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12577,62 +13349,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_AU_VZV_UNSPECIFIED</t>
+          <t>SER_FI_THL_TTR_1501</t>
         </is>
       </c>
       <c r="AT84" t="n">
         <v>1</v>
       </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12664,12 +13504,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12703,13 +13543,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>282</v>
+        <v>1920</v>
       </c>
       <c r="O85" t="n">
-        <v>282</v>
+        <v>1920</v>
       </c>
       <c r="R85" t="n">
-        <v>9.107874047791146</v>
+        <v>7.051798693477997</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -12723,7 +13563,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
@@ -12746,12 +13586,12 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -12766,12 +13606,12 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
@@ -12808,12 +13648,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12847,17 +13687,17 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O86" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="R86" t="n">
-        <v>1.067285502518482</v>
+        <v>5.309720055221089</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12867,7 +13707,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
@@ -12877,7 +13717,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -12885,42 +13725,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12952,12 +13792,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12982,22 +13822,22 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1595</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1595</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>5.858134852134065</v>
+        <v>0</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -13034,12 +13874,12 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -13054,12 +13894,12 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
@@ -13096,12 +13936,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13126,26 +13966,26 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="O88" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="R88" t="n">
-        <v>0.9427688605579929</v>
+        <v>1.859434211358168</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13155,7 +13995,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
@@ -13165,7 +14005,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1501</t>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -13173,40 +14013,1690 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>600</v>
+      </c>
+      <c r="O89" t="n">
+        <v>600</v>
+      </c>
+      <c r="R89" t="n">
+        <v>10.45394332324934</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>164</v>
+      </c>
+      <c r="O90" t="n">
+        <v>164</v>
+      </c>
+      <c r="R90" t="n">
+        <v>8.555765855816565</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>26</v>
+      </c>
+      <c r="O91" t="n">
+        <v>26</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4.477424310003082</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>861</v>
+      </c>
+      <c r="O92" t="n">
+        <v>861</v>
+      </c>
+      <c r="R92" t="n">
+        <v>12.03485327053777</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>282</v>
+      </c>
+      <c r="O93" t="n">
+        <v>282</v>
+      </c>
+      <c r="R93" t="n">
+        <v>9.107874047791146</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>60</v>
+      </c>
+      <c r="O94" t="n">
+        <v>60</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.067285502518482</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW88" t="inlineStr">
+      <c r="AW94" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
+      <c r="AX94" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY88" t="inlineStr">
+      <c r="AY94" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
+      <c r="AZ94" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA88" t="inlineStr">
+      <c r="BA94" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB88" t="inlineStr">
+      <c r="BB94" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC88" t="inlineStr">
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>60</v>
+      </c>
+      <c r="O95" t="n">
+        <v>60</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>1595</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1595</v>
+      </c>
+      <c r="R96" t="n">
+        <v>5.858134852134065</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_AU_VZV_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>55</v>
+      </c>
+      <c r="O97" t="n">
+        <v>55</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.9783450439752756</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>varicella-zoster-virus-infection-unspecified</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D213</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Varicella-zoster virus infection unspecified</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>水痘-带状疱疹病毒感染未分型</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>55</v>
+      </c>
+      <c r="O98" t="n">
+        <v>55</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Varicella zoster virus</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not distinguish chickenpox from zoster; map to unspecified VZV concept.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1501</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -13338,7 +15828,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -13358,7 +15848,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -13368,7 +15858,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13390,7 +15880,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27604</v>
+        <v>27606</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d213/2026-2029.xlsx
+++ b/diseases/d213/2026-2029.xlsx
@@ -34315,13 +34315,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O173" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R173" t="n">
-        <v>0.9783450439752756</v>
+        <v>1.067285502518482</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -34474,10 +34474,10 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O174" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27605</v>
+        <v>27610</v>
       </c>
     </row>
     <row r="16">
